--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -1192,14 +1192,14 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -1220,14 +1220,14 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1332,14 +1332,14 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1388,14 +1388,14 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1500,14 +1500,14 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1556,14 +1556,14 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1724,14 +1724,14 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1752,14 +1752,14 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1780,14 +1780,14 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1808,14 +1808,14 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1836,14 +1836,14 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1948,14 +1948,14 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1976,14 +1976,14 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2032,14 +2032,14 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2088,14 +2088,14 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2116,14 +2116,14 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2200,14 +2200,14 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2256,14 +2256,14 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2312,14 +2312,14 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -2340,14 +2340,14 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2368,14 +2368,14 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -2396,14 +2396,14 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -2452,14 +2452,14 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -2508,14 +2508,14 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -2536,14 +2536,14 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -2564,14 +2564,14 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -2648,14 +2648,14 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -2704,14 +2704,14 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -2732,14 +2732,14 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -2760,14 +2760,14 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
+          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/b9cc4ebd5957b88060059dc2a7e3b08364ab3dca/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948+00:00</t>
+          <t>2026-09-25T05:02:58.124992+00:00</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24T12:48:45.947948Z</t>
+          <t>2026-09-25T05:02:58.124992Z</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -10885,7 +10885,7 @@
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>deb37ecf6bc37a4862d78515fa35d8a4dc38bcdd</t>
+          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
         </is>
       </c>
     </row>

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -1192,14 +1192,14 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -1220,14 +1220,14 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1332,14 +1332,14 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1388,14 +1388,14 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1500,14 +1500,14 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1556,14 +1556,14 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1668,14 +1668,14 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1724,14 +1724,14 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1752,14 +1752,14 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1780,14 +1780,14 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1808,14 +1808,14 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1836,14 +1836,14 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1948,14 +1948,14 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1976,14 +1976,14 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2032,14 +2032,14 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2088,14 +2088,14 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2116,14 +2116,14 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2200,14 +2200,14 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2256,14 +2256,14 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2312,14 +2312,14 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -2340,14 +2340,14 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2368,14 +2368,14 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -2396,14 +2396,14 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -2452,14 +2452,14 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -2508,14 +2508,14 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -2536,14 +2536,14 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -2564,14 +2564,14 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -2648,14 +2648,14 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -2704,14 +2704,14 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -2732,14 +2732,14 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -2760,14 +2760,14 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/b9cc4ebd5957b88060059dc2a7e3b08364ab3dca/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
+          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/d21e69eecf3c47e3a74d992d6e2032b6bd570bb4/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992+00:00</t>
+          <t>2026-09-25T21:34:10.649390+00:00</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25T05:02:58.124992Z</t>
+          <t>2026-09-25T21:34:10.649390Z</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -10885,7 +10885,7 @@
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>b9cc4ebd5957b88060059dc2a7e3b08364ab3dca</t>
+          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
         </is>
       </c>
     </row>

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -371,8 +371,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I61" headerRowCount="1">
-  <autoFilter ref="A1:I61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I65" headerRowCount="1">
+  <autoFilter ref="A1:I65"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Change ID"/>
     <tableColumn id="2" name="Changed At"/>
@@ -403,8 +403,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ServiceUpdates" displayName="ServiceUpdates" ref="A1:J8" headerRowCount="1">
-  <autoFilter ref="A1:J8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ServiceUpdates" displayName="ServiceUpdates" ref="A1:J10" headerRowCount="1">
+  <autoFilter ref="A1:J10"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Version"/>
     <tableColumn id="2" name="Release Label"/>
@@ -458,8 +458,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="KeyDates" displayName="KeyDates" ref="A1:K216" headerRowCount="1">
-  <autoFilter ref="A1:K216"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="KeyDates" displayName="KeyDates" ref="A1:K228" headerRowCount="1">
+  <autoFilter ref="A1:K228"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Start Date"/>
     <tableColumn id="2" name="End Date"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-08T10:33:21.166559Z</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4140,6 +4140,186 @@
       <c r="I61" s="7" t="inlineStr">
         <is>
           <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>9b947246f5e3d050c568</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:33:21.166559Z</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>service_updates#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>{"text_sha256":"021c624a18c2f71c97e45351252ccad39143369fb3e71b83403d4958f17724ba","title":"Targeted release schedule (dates subject to change)","url":"https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change"}</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>{"text_sha256":"8fe3824b5426e5a32b5fcd703af44cca6d8de2408f6064f2869c957d5a82992a","title":"Targeted release schedule (dates subject to change)","url":"https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change"}</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>d674a30d44a585ac155e</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:33:21.166559Z</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>service_update</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>{"end_of_service_date":"2028-02-15","first_autoupdate_date":"2027-07-02","general_availability_date":"2027-06-04","is_major":false,"preview_date":"2027-04-23","preview_latest_update_date":"2027-05-10","release_label":"CY27Q3","second_autoupdate_date":"2027-07-20"}</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>e4103484a7a3b6582408</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:33:21.166559Z</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>service_update</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>{"end_of_service_date":"2028-05-20","first_autoupdate_date":"2027-10-01","general_availability_date":"2027-09-10","is_major":false,"preview_date":"2027-07-26","preview_latest_update_date":"2027-08-16","release_label":"CY27Q4","second_autoupdate_date":"2027-10-29"}</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>c17fb3afaac493a66400</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:33:21.166559Z</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>service_update</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49#second_autoupdate_date</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4510,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832+00:00</t>
+          <t>2026-10-08T10:33:21.166559+00:00</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4556,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4719,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-08T10:33:21.166559Z</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4731,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-08T10:33:21.166559Z</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4743,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-08T10:33:21.166559Z</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4755,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-08T10:33:21.166559Z</t>
         </is>
       </c>
     </row>
@@ -4821,7 +5001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4922,7 +5102,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5140,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -4998,7 +5178,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5216,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -5067,14 +5247,14 @@
         <v>46297</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>46327</v>
+        <v>46325</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>46528</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5292,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5330,83 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>d21e69eecf3c47e3a74d992d6e2032b6bd570bb4</t>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CY27Q3</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>46500</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>46517</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>46542</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>46570</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>46588</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>46798</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>CY27Q4</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>46594</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>46615</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>46640</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>46661</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>46689</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>46893</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7615,7 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>77</v>
@@ -7369,7 +7625,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>A new service update becomes generally available every 91 days, or 13 weeks (median of 6 intervals; range 77–105 days).</t>
+          <t>A new service update becomes generally available every 91 days, or 13 weeks (median of 8 intervals; range 77–105 days).</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr"/>
@@ -7409,7 +7665,7 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>42</v>
@@ -7419,7 +7675,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>General availability comes 46 days after preview availability (median of 7 service updates; range 42–63 days).</t>
+          <t>General availability comes 46 days after preview availability (median of 9 service updates; range 42–63 days).</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr"/>
@@ -7459,7 +7715,7 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>21</v>
@@ -7469,7 +7725,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>The first production autoupdate comes 21 days, or 3 weeks, after general availability (median of 7 service updates; range 21–40 days).</t>
+          <t>The first production autoupdate comes 21 days, or 3 weeks, after general availability (median of 9 service updates; range 21–40 days).</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr"/>
@@ -7509,17 +7765,17 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G37" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="H37" s="7" t="n">
-        <v>30</v>
-      </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>The second autoupdate window comes 28 days, or 4 weeks, after the first (median of 7 service updates; range 28–30 days).</t>
+          <t>The second autoupdate window comes 28 days, or 4 weeks, after the first (median of 9 service updates; range 18–28 days).</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr"/>
@@ -7559,7 +7815,7 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>238</v>
@@ -7569,7 +7825,7 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>End of service comes 252 days, or 36 weeks, after general availability (median of 7 service updates; range 238–256 days).</t>
+          <t>End of service comes 252 days, or 36 weeks, after general availability (median of 9 service updates; range 238–256 days).</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr"/>
@@ -7600,7 +7856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14139,48 +14395,38 @@
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B148" s="8" t="n">
-        <v>46327</v>
+        <v>46325</v>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 5 production</t>
+          <t>10.0.49 second autoupdate (production)</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>10.0.47-PQU-14</t>
-        </is>
-      </c>
+          <t>autoupdate_second</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="n"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G148" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
-        </is>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="7" t="n"/>
       <c r="I148" s="7" t="inlineStr"/>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-5</t>
+          <t>autoupdate_second:10.0.49</t>
         </is>
       </c>
     </row>
@@ -14193,7 +14439,7 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 6 production</t>
+          <t>10.0.47 PQU-14 · Station 5 production</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -14212,7 +14458,7 @@
         </is>
       </c>
       <c r="G149" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
@@ -14227,7 +14473,7 @@
       </c>
       <c r="K149" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-6</t>
+          <t>production_window:10.0.47-PQU-14:station-5</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14486,7 @@
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 5 production</t>
+          <t>10.0.47 PQU-14 · Station 6 production</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -14250,16 +14496,16 @@
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G150" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -14274,7 +14520,7 @@
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-5</t>
+          <t>production_window:10.0.47-PQU-14:station-6</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14533,7 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 6 production</t>
+          <t>10.0.49 PQU-1 · Station 5 production</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -14306,7 +14552,7 @@
         </is>
       </c>
       <c r="G151" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -14321,44 +14567,54 @@
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-6</t>
+          <t>production_window:10.0.49-PQU-1:station-5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="B152" s="8" t="n">
         <v>46327</v>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 second autoupdate (production)</t>
+          <t>10.0.49 PQU-1 · Station 6 production</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="n"/>
+          <t>production_window</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49-PQU-1</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
           <t>10.0.49</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
+      <c r="G152" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
       <c r="I152" s="7" t="inlineStr"/>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second:10.0.49</t>
+          <t>production_window:10.0.49-PQU-1:station-6</t>
         </is>
       </c>
     </row>
@@ -16804,25 +17060,25 @@
     </row>
     <row r="209">
       <c r="A209" s="8" t="n">
-        <v>46507</v>
+        <v>46500</v>
       </c>
       <c r="B209" s="8" t="n">
-        <v>46507</v>
+        <v>46500</v>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>10.0.51 second autoupdate (production)</t>
+          <t>10.0.52 preview</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second</t>
+          <t>preview</t>
         </is>
       </c>
       <c r="E209" s="7" t="n"/>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>10.0.51</t>
+          <t>10.0.52</t>
         </is>
       </c>
       <c r="G209" s="7" t="n"/>
@@ -16835,52 +17091,44 @@
       </c>
       <c r="K209" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second:10.0.51</t>
+          <t>preview:10.0.52</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="8" t="n">
-        <v>46512</v>
+        <v>46507</v>
       </c>
       <c r="B210" s="8" t="n">
-        <v>46512</v>
+        <v>46507</v>
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-16 change cutoff</t>
+          <t>10.0.51 second autoupdate (production)</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
-        </is>
-      </c>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>10.0.49-PQU-16</t>
-        </is>
-      </c>
+          <t>autoupdate_second</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="n"/>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.51</t>
         </is>
       </c>
       <c r="G210" s="7" t="n"/>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
+      <c r="H210" s="7" t="n"/>
       <c r="I210" s="7" t="inlineStr"/>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.49-PQU-16</t>
+          <t>autoupdate_second:10.0.51</t>
         </is>
       </c>
     </row>
@@ -16889,16 +17137,16 @@
         <v>46512</v>
       </c>
       <c r="B211" s="8" t="n">
-        <v>46536</v>
+        <v>46512</v>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-16 train</t>
+          <t>10.0.49 PQU-16 change cutoff</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
@@ -16925,208 +17173,660 @@
       </c>
       <c r="K211" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.49-PQU-16</t>
+          <t>change_cutoff:10.0.49-PQU-16</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="8" t="n">
-        <v>46528</v>
+        <v>46512</v>
       </c>
       <c r="B212" s="8" t="n">
-        <v>46528</v>
+        <v>46536</v>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 end of service</t>
+          <t>10.0.49 PQU-16 train</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>end_of_service</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="n"/>
+          <t>train_window</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49-PQU-16</t>
+        </is>
+      </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
           <t>10.0.49</t>
         </is>
       </c>
       <c r="G212" s="7" t="n"/>
-      <c r="H212" s="7" t="n"/>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
       <c r="I212" s="7" t="inlineStr"/>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K212" s="7" t="inlineStr">
         <is>
-          <t>end_of_service:10.0.49</t>
+          <t>train_window:10.0.49-PQU-16</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="8" t="n">
-        <v>46533</v>
+        <v>46517</v>
       </c>
       <c r="B213" s="8" t="n">
-        <v>46533</v>
+        <v>46517</v>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-17 change cutoff</t>
+          <t>10.0.52 latest preview update</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="inlineStr">
-        <is>
-          <t>10.0.49-PQU-17</t>
-        </is>
-      </c>
+          <t>preview_latest_update</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="n"/>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.52</t>
         </is>
       </c>
       <c r="G213" s="7" t="n"/>
-      <c r="H213" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
+      <c r="H213" s="7" t="n"/>
       <c r="I213" s="7" t="inlineStr"/>
       <c r="J213" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K213" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.49-PQU-17</t>
+          <t>preview_latest_update:10.0.52</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="8" t="n">
-        <v>46533</v>
+        <v>46528</v>
       </c>
       <c r="B214" s="8" t="n">
-        <v>46557</v>
+        <v>46528</v>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-17 train</t>
+          <t>10.0.49 end of service</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="inlineStr">
-        <is>
-          <t>10.0.49-PQU-17</t>
-        </is>
-      </c>
+          <t>end_of_service</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="n"/>
       <c r="F214" s="7" t="inlineStr">
         <is>
           <t>10.0.49</t>
         </is>
       </c>
       <c r="G214" s="7" t="n"/>
-      <c r="H214" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
+      <c r="H214" s="7" t="n"/>
       <c r="I214" s="7" t="inlineStr"/>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K214" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.49-PQU-17</t>
+          <t>end_of_service:10.0.49</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="8" t="n">
-        <v>46619</v>
+        <v>46533</v>
       </c>
       <c r="B215" s="8" t="n">
-        <v>46619</v>
+        <v>46533</v>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>10.0.50 end of service</t>
+          <t>10.0.49 PQU-17 change cutoff</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>end_of_service</t>
-        </is>
-      </c>
-      <c r="E215" s="7" t="n"/>
+          <t>change_cutoff</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49-PQU-17</t>
+        </is>
+      </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>10.0.50</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G215" s="7" t="n"/>
-      <c r="H215" s="7" t="n"/>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
       <c r="I215" s="7" t="inlineStr"/>
       <c r="J215" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
-          <t>end_of_service:10.0.50</t>
+          <t>change_cutoff:10.0.49-PQU-17</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="8" t="n">
-        <v>46710</v>
+        <v>46533</v>
       </c>
       <c r="B216" s="8" t="n">
-        <v>46710</v>
+        <v>46557</v>
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>10.0.51 end of service</t>
+          <t>10.0.49 PQU-17 train</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>end_of_service</t>
-        </is>
-      </c>
-      <c r="E216" s="7" t="n"/>
+          <t>train_window</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49-PQU-17</t>
+        </is>
+      </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>10.0.51</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G216" s="7" t="n"/>
-      <c r="H216" s="7" t="n"/>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
       <c r="I216" s="7" t="inlineStr"/>
       <c r="J216" s="7" t="inlineStr">
         <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+        </is>
+      </c>
+      <c r="K216" s="7" t="inlineStr">
+        <is>
+          <t>train_window:10.0.49-PQU-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="n">
+        <v>46542</v>
+      </c>
+      <c r="B217" s="8" t="n">
+        <v>46542</v>
+      </c>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52 general availability</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>general_availability</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="n"/>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="n"/>
+      <c r="H217" s="7" t="n"/>
+      <c r="I217" s="7" t="inlineStr"/>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
           <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
-      <c r="K216" s="7" t="inlineStr">
+      <c r="K217" s="7" t="inlineStr">
+        <is>
+          <t>general_availability:10.0.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="n">
+        <v>46570</v>
+      </c>
+      <c r="B218" s="8" t="n">
+        <v>46570</v>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52 first autoupdate (production)</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_first</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="n"/>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="n"/>
+      <c r="H218" s="7" t="n"/>
+      <c r="I218" s="7" t="inlineStr"/>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K218" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_first:10.0.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="n">
+        <v>46588</v>
+      </c>
+      <c r="B219" s="8" t="n">
+        <v>46588</v>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52 second autoupdate (production)</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_second</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="n"/>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n"/>
+      <c r="H219" s="7" t="n"/>
+      <c r="I219" s="7" t="inlineStr"/>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_second:10.0.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="n">
+        <v>46594</v>
+      </c>
+      <c r="B220" s="8" t="n">
+        <v>46594</v>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 preview</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>preview</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="n"/>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n"/>
+      <c r="H220" s="7" t="n"/>
+      <c r="I220" s="7" t="inlineStr"/>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K220" s="7" t="inlineStr">
+        <is>
+          <t>preview:10.0.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="n">
+        <v>46615</v>
+      </c>
+      <c r="B221" s="8" t="n">
+        <v>46615</v>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 latest preview update</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>preview_latest_update</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="n"/>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n"/>
+      <c r="H221" s="7" t="n"/>
+      <c r="I221" s="7" t="inlineStr"/>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>preview_latest_update:10.0.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="n">
+        <v>46619</v>
+      </c>
+      <c r="B222" s="8" t="n">
+        <v>46619</v>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>10.0.50 end of service</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="n"/>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>10.0.50</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n"/>
+      <c r="H222" s="7" t="n"/>
+      <c r="I222" s="7" t="inlineStr"/>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K222" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service:10.0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="n">
+        <v>46640</v>
+      </c>
+      <c r="B223" s="8" t="n">
+        <v>46640</v>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 general availability</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>general_availability</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="n"/>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n"/>
+      <c r="H223" s="7" t="n"/>
+      <c r="I223" s="7" t="inlineStr"/>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>general_availability:10.0.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B224" s="8" t="n">
+        <v>46661</v>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 first autoupdate (production)</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_first</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="n"/>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n"/>
+      <c r="H224" s="7" t="n"/>
+      <c r="I224" s="7" t="inlineStr"/>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K224" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_first:10.0.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="n">
+        <v>46689</v>
+      </c>
+      <c r="B225" s="8" t="n">
+        <v>46689</v>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 second autoupdate (production)</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_second</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="n"/>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n"/>
+      <c r="H225" s="7" t="n"/>
+      <c r="I225" s="7" t="inlineStr"/>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K225" s="7" t="inlineStr">
+        <is>
+          <t>autoupdate_second:10.0.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="n">
+        <v>46710</v>
+      </c>
+      <c r="B226" s="8" t="n">
+        <v>46710</v>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>10.0.51 end of service</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="n"/>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>10.0.51</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="n"/>
+      <c r="H226" s="7" t="n"/>
+      <c r="I226" s="7" t="inlineStr"/>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K226" s="7" t="inlineStr">
         <is>
           <t>end_of_service:10.0.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="n">
+        <v>46798</v>
+      </c>
+      <c r="B227" s="8" t="n">
+        <v>46798</v>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52 end of service</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="n"/>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="n"/>
+      <c r="H227" s="7" t="n"/>
+      <c r="I227" s="7" t="inlineStr"/>
+      <c r="J227" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service:10.0.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="n">
+        <v>46893</v>
+      </c>
+      <c r="B228" s="8" t="n">
+        <v>46893</v>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53 end of service</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="n"/>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>10.0.53</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="n"/>
+      <c r="H228" s="7" t="n"/>
+      <c r="I228" s="7" t="inlineStr"/>
+      <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+        </is>
+      </c>
+      <c r="K228" s="7" t="inlineStr">
+        <is>
+          <t>end_of_service:10.0.53</t>
         </is>
       </c>
     </row>

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -371,8 +371,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I65" headerRowCount="1">
-  <autoFilter ref="A1:I65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I66" headerRowCount="1">
+  <autoFilter ref="A1:I66"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Change ID"/>
     <tableColumn id="2" name="Changed At"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559Z</t>
+          <t>2026-10-08T19:14:10.623818Z</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4320,6 +4320,53 @@
       <c r="I65" s="7" t="inlineStr">
         <is>
           <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>051f5ffbd31f0dea8f3e</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08T19:14:10.623818Z</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>service_update</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>10.0.52#second_autoupdate_date</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>2027-07-20</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4557,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559+00:00</t>
+          <t>2026-10-08T19:14:10.623818+00:00</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4603,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4766,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559Z</t>
+          <t>2026-10-08T19:14:10.623818Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4778,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559Z</t>
+          <t>2026-10-08T19:14:10.623818Z</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4790,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559Z</t>
+          <t>2026-10-08T19:14:10.623818Z</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4802,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T10:33:21.166559Z</t>
+          <t>2026-10-08T19:14:10.623818Z</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5149,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5187,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5225,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5263,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5301,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5339,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5377,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5361,14 +5408,14 @@
         <v>46570</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>46588</v>
+        <v>46598</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>46798</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5453,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>c4987ba4b48273d8a2f2ea0e54f8769dbeb3b5a2</t>
+          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7815,14 @@
         <v>9</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>28</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>The second autoupdate window comes 28 days, or 4 weeks, after the first (median of 9 service updates; range 18–28 days).</t>
+          <t>The second autoupdate window comes 28 days, or 4 weeks, after the first (median of 9 service updates).</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr"/>
@@ -17462,25 +17509,25 @@
     </row>
     <row r="219">
       <c r="A219" s="8" t="n">
-        <v>46588</v>
+        <v>46594</v>
       </c>
       <c r="B219" s="8" t="n">
-        <v>46588</v>
+        <v>46594</v>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>10.0.52 second autoupdate (production)</t>
+          <t>10.0.53 preview</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second</t>
+          <t>preview</t>
         </is>
       </c>
       <c r="E219" s="7" t="n"/>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>10.0.52</t>
+          <t>10.0.53</t>
         </is>
       </c>
       <c r="G219" s="7" t="n"/>
@@ -17493,31 +17540,31 @@
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second:10.0.52</t>
+          <t>preview:10.0.53</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="8" t="n">
-        <v>46594</v>
+        <v>46598</v>
       </c>
       <c r="B220" s="8" t="n">
-        <v>46594</v>
+        <v>46598</v>
       </c>
       <c r="C220" s="7" t="inlineStr">
         <is>
-          <t>10.0.53 preview</t>
+          <t>10.0.52 second autoupdate (production)</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>preview</t>
+          <t>autoupdate_second</t>
         </is>
       </c>
       <c r="E220" s="7" t="n"/>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>10.0.53</t>
+          <t>10.0.52</t>
         </is>
       </c>
       <c r="G220" s="7" t="n"/>
@@ -17530,7 +17577,7 @@
       </c>
       <c r="K220" s="7" t="inlineStr">
         <is>
-          <t>preview:10.0.53</t>
+          <t>autoupdate_second:10.0.52</t>
         </is>
       </c>
     </row>

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -371,8 +371,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I66" headerRowCount="1">
-  <autoFilter ref="A1:I66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChangeHistory" displayName="ChangeHistory" ref="A1:I86" headerRowCount="1">
+  <autoFilter ref="A1:I86"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Change ID"/>
     <tableColumn id="2" name="Changed At"/>
@@ -507,8 +507,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="UpcomingPqu" displayName="UpcomingPqu" ref="A1:T30" headerRowCount="1">
-  <autoFilter ref="A1:T30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="UpcomingPqu" displayName="UpcomingPqu" ref="A1:T29" headerRowCount="1">
+  <autoFilter ref="A1:T29"/>
   <tableColumns count="20">
     <tableColumn id="1" name="PQU ID"/>
     <tableColumn id="2" name="Application Version"/>
@@ -617,8 +617,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="StatusHistory" displayName="StatusHistory" ref="A1:F7" headerRowCount="1">
-  <autoFilter ref="A1:F7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="StatusHistory" displayName="StatusHistory" ref="A1:F9" headerRowCount="1">
+  <autoFilter ref="A1:F9"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Changed At"/>
     <tableColumn id="2" name="PQU ID"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>a602e92c9987dcdd9320df9a3a6e349e6c065fa3d7e8cd38ccd24ea6f03a959b</t>
+          <t>8431bf5fb97becf088a0eaa4eec8f42cb7f86dcafc7f68f9d4b3d972b5cf1eb0</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1459,6 +1459,70 @@
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4367,6 +4431,874 @@
       <c r="I66" s="7" t="inlineStr">
         <is>
           <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>a6a5409b0154676b85e5</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>94e5471ceebae1ddee34</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>uep_version</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48.7</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>fe07b260909e997c00b0</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>station_schedule_available</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>56c230edd4a7de5904d2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>44216ccbc5b43857dd7f</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>application_build</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>10.0.2645.158</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>4e8475bc0837b9bd811d</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>platform_build</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>7.0.7996.126</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>29bed797987a236ed099</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>uep_version</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48.9</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>956d6975812e26a3e48a</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>pqu</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>station_schedule_available</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>500559dfb8ac4bae4450</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>station.1</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":null,"production_start_date":null,"sandbox_end_date":"2026-10-17","sandbox_start_date":"2026-10-14"}</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>60200c5364e65e4932c6</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>station.2</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-10-25","production_start_date":"2026-10-24","sandbox_end_date":"2026-10-22","sandbox_start_date":"2026-10-19"}</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>d6cbe63bc9d8f57a5452</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>station.3</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-10-25","production_start_date":"2026-10-24","sandbox_end_date":"2026-10-22","sandbox_start_date":"2026-10-19"}</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>c93a90453c045fad6ec5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>station.4</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-11-01","production_start_date":"2026-10-31","sandbox_end_date":"2026-10-29","sandbox_start_date":"2026-10-26"}</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>6929df44a73687f54d53</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>station.5</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-11-08","production_start_date":"2026-11-07","sandbox_end_date":"2026-11-05","sandbox_start_date":"2026-11-02"}</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>9a607bd19bd2147af80f</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-8</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>station.6</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-11-08","production_start_date":"2026-11-07","sandbox_end_date":"2026-11-05","sandbox_start_date":"2026-11-02"}</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>ecc9cf1ceaad450df243</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>station.1</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":null,"production_start_date":null,"sandbox_end_date":"2026-09-19","sandbox_start_date":"2026-09-16"}</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>227605b7abcc53c8f353</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>station.2</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-09-27","production_start_date":"2026-09-26","sandbox_end_date":"2026-09-24","sandbox_start_date":"2026-09-21"}</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>65007bc60a56c8ad0433</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>station.3</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-09-27","production_start_date":"2026-09-26","sandbox_end_date":"2026-09-24","sandbox_start_date":"2026-09-21"}</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>1d7d96b237b0f07f6dd0</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>station.4</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-10-04","production_start_date":"2026-10-03","sandbox_end_date":"2026-10-01","sandbox_start_date":"2026-09-28"}</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>9119be15fdc6bf05d14d</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>station.5</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-10-11","production_start_date":"2026-10-10","sandbox_end_date":"2026-10-08","sandbox_start_date":"2026-10-05"}</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>f220235cd2984150bad4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48-PQU-6</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>station</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>station.6</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>{"production_end_date":"2026-10-11","production_start_date":"2026-10-10","sandbox_end_date":"2026-10-08","sandbox_start_date":"2026-10-05"}</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -4485,7 +5417,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -4509,7 +5441,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/aee43141bb5f24e63c1e63805dcd9e1c5452c334/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
+          <t>https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/7d86a35169692606d303c21e204ae6032d44d44e/articles/fin-ops-core/dev-itpro/get-started/quality-updates-schedule.md</t>
         </is>
       </c>
     </row>
@@ -4521,7 +5453,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4533,7 +5465,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>a602e92c9987dcdd9320df9a3a6e349e6c065fa3d7e8cd38ccd24ea6f03a959b</t>
+          <t>8431bf5fb97becf088a0eaa4eec8f42cb7f86dcafc7f68f9d4b3d972b5cf1eb0</t>
         </is>
       </c>
     </row>
@@ -4545,7 +5477,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:14:25.524832Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -4557,7 +5489,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818+00:00</t>
+          <t>2026-10-13T13:44:17.669863+00:00</t>
         </is>
       </c>
     </row>
@@ -4766,7 +5698,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -4778,7 +5710,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -4790,7 +5722,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5734,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:14:10.623818Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
     </row>
@@ -4863,7 +5795,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -4894,7 +5826,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -4906,7 +5838,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>a602e92c9987dcdd9320df9a3a6e349e6c065fa3d7e8cd38ccd24ea6f03a959b</t>
+          <t>8431bf5fb97becf088a0eaa4eec8f42cb7f86dcafc7f68f9d4b3d972b5cf1eb0</t>
         </is>
       </c>
     </row>
@@ -6101,12 +7033,12 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>10.0.46-PQU-1: Source warning: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
+          <t>10.0.46-PQU-1: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose start date has a source warning is left out, together with the intervals next to it.</t>
+          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose published start date contradicts Microsoft's other published dates is left out, together with the intervals next to it.</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -6156,7 +7088,7 @@
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose start date has a source warning is left out, together with the intervals next to it.</t>
+          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose published start date contradicts Microsoft's other published dates is left out, together with the intervals next to it.</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -6206,7 +7138,7 @@
       <c r="J4" s="7" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose start date has a source warning is left out, together with the intervals next to it.</t>
+          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose published start date contradicts Microsoft's other published dates is left out, together with the intervals next to it.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -6256,7 +7188,7 @@
       <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose start date has a source warning is left out, together with the intervals next to it.</t>
+          <t>The trains of each application version are put in train-number order. For each pair of consecutive train numbers, the days between their published start dates are counted, and the figure is the median. A train whose published start date contradicts Microsoft's other published dates is left out, together with the intervals next to it.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6305,12 +7237,12 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>10.0.46-PQU-1: Source warning: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
+          <t>10.0.46-PQU-1: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6360,7 +7292,7 @@
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -6410,7 +7342,7 @@
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -6460,7 +7392,7 @@
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>For each train, the days from its published change cutoff date to its published start date. The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -6509,12 +7441,12 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>10.0.46-PQU-1: Source warning: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
+          <t>10.0.46-PQU-1: Change cutoff 2026-02-04 and train start 2025-02-09 are in different years</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -6564,7 +7496,7 @@
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -6614,7 +7546,7 @@
       <c r="J12" s="7" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -6664,7 +7596,7 @@
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains with a source warning on either date are left out.</t>
+          <t>Calendar days from each train's published start date to its published end date, counting both dates (the same count as “Day X of Y” on the Trains tab). The figure is the median per application version. Trains whose published dates contradict Microsoft's other published dates are left out.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -6796,7 +7728,7 @@
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>10.0.48: 17 trains: 2 In-Progress, 10 Not Started, 5 Completed.</t>
+          <t>10.0.48: 17 trains: 2 In-Progress, 9 Not Started, 6 Completed.</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -11189,7 +12121,7 @@
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr"/>
@@ -11234,7 +12166,7 @@
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr"/>
@@ -11251,34 +12183,32 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B79" s="8" t="n">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 1 sandbox</t>
+          <t>10.0.47 PQU-13 change cutoff</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11287,45 +12217,43 @@
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-1</t>
+          <t>change_cutoff:10.0.47-PQU-13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B80" s="8" t="n">
-        <v>46289</v>
+        <v>46312</v>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 2 sandbox</t>
+          <t>10.0.47 PQU-13 train</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>2</v>
-      </c>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11334,25 +12262,25 @@
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-2</t>
+          <t>train_window:10.0.47-PQU-13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B81" s="8" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 3 sandbox</t>
+          <t>10.0.47 PQU-13 · Station 1 sandbox</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -11362,16 +12290,16 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -11386,25 +12314,25 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-3</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B82" s="8" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 change cutoff</t>
+          <t>10.0.47 PQU-13 · Station 2 sandbox</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -11417,7 +12345,9 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n"/>
+      <c r="G82" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11426,30 +12356,30 @@
       <c r="I82" s="7" t="inlineStr"/>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.47-PQU-13</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B83" s="8" t="n">
-        <v>46312</v>
+        <v>46296</v>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 train</t>
+          <t>10.0.47 PQU-13 · Station 3 sandbox</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -11462,7 +12392,9 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n"/>
+      <c r="G83" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11471,45 +12403,43 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.47-PQU-13</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B84" s="8" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 1 sandbox</t>
+          <t>10.0.48 PQU-7 change cutoff</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11518,35 +12448,35 @@
       <c r="I84" s="7" t="inlineStr"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-1</t>
+          <t>change_cutoff:10.0.48-PQU-7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B85" s="8" t="n">
-        <v>46292</v>
+        <v>46319</v>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 2 production</t>
+          <t>10.0.48 PQU-7 train</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -11554,9 +12484,7 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11565,35 +12493,35 @@
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-6:station-2</t>
+          <t>train_window:10.0.48-PQU-7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B86" s="8" t="n">
-        <v>46292</v>
+        <v>46298</v>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 3 production</t>
+          <t>10.0.48 PQU-7 · Station 1 sandbox</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -11602,7 +12530,7 @@
         </is>
       </c>
       <c r="G86" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -11617,72 +12545,62 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-6:station-3</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B87" s="8" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 2 sandbox</t>
+          <t>10.0.49 first autoupdate (production)</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>10.0.47-PQU-13</t>
-        </is>
-      </c>
+          <t>autoupdate_first</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
-        </is>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-2</t>
+          <t>autoupdate_first:10.0.49</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="B88" s="8" t="n">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 3 sandbox</t>
+          <t>10.0.47 PQU-13 · Station 2 production</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -11696,7 +12614,7 @@
         </is>
       </c>
       <c r="G88" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -11711,39 +12629,39 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-3</t>
+          <t>production_window:10.0.47-PQU-13:station-2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="B89" s="8" t="n">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 4 sandbox</t>
+          <t>10.0.47 PQU-13 · Station 3 production</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -11758,38 +12676,40 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-4</t>
+          <t>production_window:10.0.47-PQU-13:station-3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B90" s="8" t="n">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 change cutoff</t>
+          <t>10.0.47 PQU-13 · Station 4 sandbox</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="n"/>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11798,30 +12718,30 @@
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.48-PQU-7</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B91" s="8" t="n">
-        <v>46319</v>
+        <v>46303</v>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 train</t>
+          <t>10.0.48 PQU-7 · Station 2 sandbox</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -11834,7 +12754,9 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n"/>
+      <c r="G91" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11843,25 +12765,25 @@
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.48-PQU-7</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B92" s="8" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 1 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 3 sandbox</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -11880,7 +12802,7 @@
         </is>
       </c>
       <c r="G92" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -11895,77 +12817,83 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-1</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="B93" s="8" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 first autoupdate (production)</t>
+          <t>10.0.47 PQU-14 change cutoff</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_first</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n"/>
+          <t>change_cutoff</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>10.0.47-PQU-14</t>
+        </is>
+      </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
       <c r="I93" s="7" t="inlineStr"/>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_first:10.0.49</t>
+          <t>change_cutoff:10.0.47-PQU-14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B94" s="8" t="n">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 2 production</t>
+          <t>10.0.49 PQU-1 change cutoff</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="n">
-        <v>2</v>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -11974,35 +12902,35 @@
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-13:station-2</t>
+          <t>change_cutoff:10.0.49-PQU-1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B95" s="8" t="n">
-        <v>46299</v>
+        <v>46326</v>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 3 production</t>
+          <t>10.0.47 PQU-14 train</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -12010,9 +12938,7 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12021,45 +12947,43 @@
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-13:station-3</t>
+          <t>train_window:10.0.47-PQU-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B96" s="8" t="n">
-        <v>46299</v>
+        <v>46326</v>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 4 production</t>
+          <t>10.0.49 PQU-1 train</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="n">
-        <v>4</v>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12068,25 +12992,25 @@
       <c r="I96" s="7" t="inlineStr"/>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-6:station-4</t>
+          <t>train_window:10.0.49-PQU-1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B97" s="8" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 4 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 1 sandbox</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -12096,7 +13020,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -12105,7 +13029,7 @@
         </is>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -12120,20 +13044,20 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-4</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B98" s="8" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 5 sandbox</t>
+          <t>10.0.49 PQU-1 · Station 1 sandbox</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -12143,16 +13067,16 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G98" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -12167,39 +13091,39 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-5</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="B99" s="8" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 6 sandbox</t>
+          <t>10.0.47 PQU-13 · Station 4 production</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G99" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -12214,25 +13138,25 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-6:station-6</t>
+          <t>production_window:10.0.47-PQU-13:station-4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="B100" s="8" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 2 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 2 production</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -12261,25 +13185,25 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-2</t>
+          <t>production_window:10.0.48-PQU-7:station-2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="B101" s="8" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 3 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 3 production</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -12308,30 +13232,30 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-3</t>
+          <t>production_window:10.0.48-PQU-7:station-3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B102" s="8" t="n">
-        <v>46302</v>
+        <v>46310</v>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 change cutoff</t>
+          <t>10.0.47 PQU-13 · Station 5 sandbox</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -12339,7 +13263,9 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n"/>
+      <c r="G102" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12348,43 +13274,45 @@
       <c r="I102" s="7" t="inlineStr"/>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.47-PQU-14</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B103" s="8" t="n">
-        <v>46302</v>
+        <v>46310</v>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 change cutoff</t>
+          <t>10.0.47 PQU-13 · Station 6 sandbox</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="n"/>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12393,30 +13321,30 @@
       <c r="I103" s="7" t="inlineStr"/>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.49-PQU-1</t>
+          <t>sandbox_window:10.0.47-PQU-13:station-6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B104" s="8" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 train</t>
+          <t>10.0.47 PQU-14 · Station 2 sandbox</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -12429,7 +13357,9 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n"/>
+      <c r="G104" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12438,43 +13368,45 @@
       <c r="I104" s="7" t="inlineStr"/>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.47-PQU-14</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B105" s="8" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 train</t>
+          <t>10.0.47 PQU-14 · Station 3 sandbox</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="n"/>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12483,25 +13415,25 @@
       <c r="I105" s="7" t="inlineStr"/>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.49-PQU-1</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B106" s="8" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 1 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 4 sandbox</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -12511,16 +13443,16 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G106" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -12535,20 +13467,20 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-1</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B107" s="8" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 1 sandbox</t>
+          <t>10.0.49 PQU-1 · Station 2 sandbox</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -12567,7 +13499,7 @@
         </is>
       </c>
       <c r="G107" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -12582,39 +13514,39 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-1</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="B108" s="8" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 4 production</t>
+          <t>10.0.49 PQU-1 · Station 3 sandbox</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G108" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -12629,30 +13561,30 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-13:station-4</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="B109" s="8" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 5 production</t>
+          <t>10.0.48 PQU-8 change cutoff</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -12660,9 +13592,7 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
-        <v>5</v>
-      </c>
+      <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12671,35 +13601,35 @@
       <c r="I109" s="7" t="inlineStr"/>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-6:station-5</t>
+          <t>change_cutoff:10.0.48-PQU-8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="B110" s="8" t="n">
-        <v>46306</v>
+        <v>46333</v>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-6 · Station 6 production</t>
+          <t>10.0.48 PQU-8 train</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -12707,9 +13637,7 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
-        <v>6</v>
-      </c>
+      <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="inlineStr">
         <is>
           <t>In-Progress</t>
@@ -12718,35 +13646,35 @@
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-6:station-6</t>
+          <t>train_window:10.0.48-PQU-8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="B111" s="8" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 2 production</t>
+          <t>10.0.48 PQU-8 · Station 1 sandbox</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -12755,7 +13683,7 @@
         </is>
       </c>
       <c r="G111" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -12770,20 +13698,20 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-7:station-2</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B112" s="8" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 3 production</t>
+          <t>10.0.47 PQU-13 · Station 5 production</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -12793,16 +13721,16 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.47-PQU-13</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G112" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -12817,25 +13745,25 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-7:station-3</t>
+          <t>production_window:10.0.47-PQU-13:station-5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B113" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 5 sandbox</t>
+          <t>10.0.47 PQU-13 · Station 6 production</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -12849,7 +13777,7 @@
         </is>
       </c>
       <c r="G113" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -12864,30 +13792,30 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-5</t>
+          <t>production_window:10.0.47-PQU-13:station-6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B114" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 6 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 2 production</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -12896,7 +13824,7 @@
         </is>
       </c>
       <c r="G114" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -12911,25 +13839,25 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-13:station-6</t>
+          <t>production_window:10.0.47-PQU-14:station-2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B115" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 2 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 3 production</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -12943,7 +13871,7 @@
         </is>
       </c>
       <c r="G115" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -12958,39 +13886,39 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-2</t>
+          <t>production_window:10.0.47-PQU-14:station-3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B116" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 3 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 4 production</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G116" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -13005,39 +13933,39 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-3</t>
+          <t>production_window:10.0.48-PQU-7:station-4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B117" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 4 sandbox</t>
+          <t>10.0.49 PQU-1 · Station 2 production</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G117" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -13052,25 +13980,25 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-4</t>
+          <t>production_window:10.0.49-PQU-1:station-2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B118" s="8" t="n">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 2 sandbox</t>
+          <t>10.0.49 PQU-1 · Station 3 production</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -13084,7 +14012,7 @@
         </is>
       </c>
       <c r="G118" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -13099,20 +14027,20 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-2</t>
+          <t>production_window:10.0.49-PQU-1:station-3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B119" s="8" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 3 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 4 sandbox</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -13122,16 +14050,16 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G119" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
@@ -13146,30 +14074,30 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-3</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="B120" s="8" t="n">
-        <v>46309</v>
+        <v>46317</v>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-8 change cutoff</t>
+          <t>10.0.48 PQU-7 · Station 5 sandbox</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-8</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -13177,44 +14105,46 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n"/>
+      <c r="G120" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr"/>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.48-PQU-8</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="B121" s="8" t="n">
-        <v>46333</v>
+        <v>46317</v>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-8 train</t>
+          <t>10.0.48 PQU-7 · Station 6 sandbox</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-8</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -13222,53 +14152,55 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n"/>
+      <c r="G121" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr"/>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.48-PQU-8</t>
+          <t>sandbox_window:10.0.48-PQU-7:station-6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B122" s="8" t="n">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 5 production</t>
+          <t>10.0.48 PQU-8 · Station 2 sandbox</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G122" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -13283,39 +14215,39 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-13:station-5</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B123" s="8" t="n">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-13 · Station 6 production</t>
+          <t>10.0.48 PQU-8 · Station 3 sandbox</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-13</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G123" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -13330,39 +14262,39 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-13:station-6</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B124" s="8" t="n">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 2 production</t>
+          <t>10.0.49 PQU-1 · Station 4 sandbox</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G124" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -13377,30 +14309,30 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-2</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B125" s="8" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 3 production</t>
+          <t>10.0.47 PQU-15 change cutoff</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.47-PQU-15</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -13408,140 +14340,134 @@
           <t>10.0.47</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr"/>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-3</t>
+          <t>change_cutoff:10.0.47-PQU-15</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B126" s="8" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 4 production</t>
+          <t>10.0.49 PQU-2 change cutoff</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.49-PQU-2</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="n">
-        <v>4</v>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-7:station-4</t>
+          <t>change_cutoff:10.0.49-PQU-2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B127" s="8" t="n">
-        <v>46313</v>
+        <v>46340</v>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 2 production</t>
+          <t>10.0.47 PQU-15 train</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-15</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="n">
-        <v>2</v>
-      </c>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n"/>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr"/>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-2</t>
+          <t>train_window:10.0.47-PQU-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B128" s="8" t="n">
-        <v>46313</v>
+        <v>46340</v>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 3 production</t>
+          <t>10.0.49 PQU-2 train</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.49-PQU-2</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -13549,102 +14475,90 @@
           <t>10.0.49</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr"/>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-3</t>
+          <t>train_window:10.0.49-PQU-2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="B129" s="8" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 4 sandbox</t>
+          <t>10.0.50 preview</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>10.0.47-PQU-14</t>
-        </is>
-      </c>
+          <t>preview</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n"/>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
-        </is>
-      </c>
+          <t>10.0.50</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="7" t="n"/>
       <c r="I129" s="7" t="inlineStr"/>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-4</t>
+          <t>preview:10.0.50</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="B130" s="8" t="n">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 5 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 4 production</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G130" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -13659,25 +14573,25 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-5</t>
+          <t>production_window:10.0.47-PQU-14:station-4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="B131" s="8" t="n">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 6 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 5 production</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
@@ -13691,7 +14605,7 @@
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -13706,39 +14620,39 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.48-PQU-7:station-6</t>
+          <t>production_window:10.0.48-PQU-7:station-5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="B132" s="8" t="n">
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 4 sandbox</t>
+          <t>10.0.48 PQU-7 · Station 6 production</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G132" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -13753,252 +14667,270 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-4</t>
+          <t>production_window:10.0.48-PQU-7:station-6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="B133" s="8" t="n">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-15 change cutoff</t>
+          <t>10.0.48 PQU-8 · Station 2 production</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-15</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="n"/>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I133" s="7" t="inlineStr"/>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.47-PQU-15</t>
+          <t>production_window:10.0.48-PQU-8:station-2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="B134" s="8" t="n">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-2 change cutoff</t>
+          <t>10.0.48 PQU-8 · Station 3 production</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-2</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="n"/>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr"/>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.49-PQU-2</t>
+          <t>production_window:10.0.48-PQU-8:station-3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="B135" s="8" t="n">
-        <v>46340</v>
+        <v>46320</v>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-15 train</t>
+          <t>10.0.49 PQU-1 · Station 4 production</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-15</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="n"/>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr"/>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.47-PQU-15</t>
+          <t>production_window:10.0.49-PQU-1:station-4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="B136" s="8" t="n">
-        <v>46340</v>
+        <v>46324</v>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-2 train</t>
+          <t>10.0.47 PQU-14 · Station 5 sandbox</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-2</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="n"/>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr"/>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.49-PQU-2</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B137" s="8" t="n">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>10.0.50 preview</t>
+          <t>10.0.47 PQU-14 · Station 6 sandbox</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>preview</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="n"/>
+          <t>sandbox_window</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>10.0.47-PQU-14</t>
+        </is>
+      </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>10.0.50</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="n"/>
-      <c r="H137" s="7" t="n"/>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
       <c r="I137" s="7" t="inlineStr"/>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>preview:10.0.50</t>
+          <t>sandbox_window:10.0.47-PQU-14:station-6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B138" s="8" t="n">
-        <v>46320</v>
+        <v>46324</v>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 4 production</t>
+          <t>10.0.48 PQU-8 · Station 4 sandbox</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G138" s="7" t="n">
@@ -14017,35 +14949,35 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-4</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B139" s="8" t="n">
-        <v>46320</v>
+        <v>46324</v>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 5 production</t>
+          <t>10.0.49 PQU-1 · Station 5 sandbox</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G139" s="7" t="n">
@@ -14064,35 +14996,35 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-7:station-5</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B140" s="8" t="n">
-        <v>46320</v>
+        <v>46324</v>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-7 · Station 6 production</t>
+          <t>10.0.49 PQU-1 · Station 6 sandbox</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="G140" s="7" t="n">
@@ -14111,176 +15043,162 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.48-PQU-7:station-6</t>
+          <t>sandbox_window:10.0.49-PQU-1:station-6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="B141" s="8" t="n">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 4 production</t>
+          <t>10.0.48 PQU-9 change cutoff</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.48-PQU-9</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="n">
-        <v>4</v>
-      </c>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n"/>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr"/>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-4</t>
+          <t>change_cutoff:10.0.48-PQU-9</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="B142" s="8" t="n">
-        <v>46324</v>
+        <v>46347</v>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 5 sandbox</t>
+          <t>10.0.48 PQU-9 train</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-9</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="n">
-        <v>5</v>
-      </c>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr"/>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-5</t>
+          <t>train_window:10.0.48-PQU-9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="B143" s="8" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 6 sandbox</t>
+          <t>10.0.49 second autoupdate (production)</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>10.0.47-PQU-14</t>
-        </is>
-      </c>
+          <t>autoupdate_second</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="n"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
-        </is>
-      </c>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="7" t="n"/>
       <c r="I143" s="7" t="inlineStr"/>
       <c r="J143" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.47-PQU-14:station-6</t>
+          <t>autoupdate_second:10.0.49</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>46321</v>
+        <v>46326</v>
       </c>
       <c r="B144" s="8" t="n">
-        <v>46324</v>
+        <v>46327</v>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 5 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 5 production</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G144" s="7" t="n">
@@ -14299,35 +15217,35 @@
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-5</t>
+          <t>production_window:10.0.47-PQU-14:station-5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n">
-        <v>46321</v>
+        <v>46326</v>
       </c>
       <c r="B145" s="8" t="n">
-        <v>46324</v>
+        <v>46327</v>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 6 sandbox</t>
+          <t>10.0.47 PQU-14 · Station 6 production</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-14</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="G145" s="7" t="n">
@@ -14346,30 +15264,30 @@
       </c>
       <c r="K145" s="7" t="inlineStr">
         <is>
-          <t>sandbox_window:10.0.49-PQU-1:station-6</t>
+          <t>production_window:10.0.47-PQU-14:station-6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="B146" s="8" t="n">
-        <v>46323</v>
+        <v>46327</v>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-9 change cutoff</t>
+          <t>10.0.48 PQU-8 · Station 4 production</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-9</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -14377,131 +15295,145 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n"/>
+      <c r="G146" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr"/>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.48-PQU-9</t>
+          <t>production_window:10.0.48-PQU-8:station-4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n">
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="B147" s="8" t="n">
-        <v>46347</v>
+        <v>46327</v>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>10.0.48 PQU-9 train</t>
+          <t>10.0.49 PQU-1 · Station 5 production</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-9</t>
+          <t>10.0.49-PQU-1</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="n"/>
+          <t>10.0.49</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr"/>
       <c r="J147" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.48-PQU-9</t>
+          <t>production_window:10.0.49-PQU-1:station-5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B148" s="8" t="n">
-        <v>46325</v>
+        <v>46327</v>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 second autoupdate (production)</t>
+          <t>10.0.49 PQU-1 · Station 6 production</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="n"/>
+          <t>production_window</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>10.0.49-PQU-1</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
           <t>10.0.49</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="7" t="n"/>
+      <c r="G148" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
       <c r="I148" s="7" t="inlineStr"/>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/public-preview-releases#targeted-release-schedule-dates-subject-to-change</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
-          <t>autoupdate_second:10.0.49</t>
+          <t>production_window:10.0.49-PQU-1:station-6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="B149" s="8" t="n">
-        <v>46327</v>
+        <v>46331</v>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 5 production</t>
+          <t>10.0.48 PQU-8 · Station 5 sandbox</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G149" s="7" t="n">
@@ -14520,35 +15452,35 @@
       </c>
       <c r="K149" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-5</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="B150" s="8" t="n">
-        <v>46327</v>
+        <v>46331</v>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-14 · Station 6 production</t>
+          <t>10.0.48 PQU-8 · Station 6 sandbox</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>sandbox_window</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-14</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="G150" s="7" t="n">
@@ -14567,77 +15499,75 @@
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.47-PQU-14:station-6</t>
+          <t>sandbox_window:10.0.48-PQU-8:station-6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n">
-        <v>46326</v>
+        <v>46330</v>
       </c>
       <c r="B151" s="8" t="n">
-        <v>46327</v>
+        <v>46330</v>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 5 production</t>
+          <t>10.0.47 PQU-16 change cutoff</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.47-PQU-16</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="n">
-        <v>5</v>
-      </c>
+          <t>10.0.47</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr"/>
       <c r="J151" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-5</t>
+          <t>change_cutoff:10.0.47-PQU-16</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>46326</v>
+        <v>46330</v>
       </c>
       <c r="B152" s="8" t="n">
-        <v>46327</v>
+        <v>46330</v>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-1 · Station 6 production</t>
+          <t>10.0.49 PQU-3 change cutoff</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>production_window</t>
+          <t>change_cutoff</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-1</t>
+          <t>10.0.49-PQU-3</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -14645,23 +15575,21 @@
           <t>10.0.49</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>6</v>
-      </c>
+      <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>In-Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr"/>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>production_window:10.0.49-PQU-1:station-6</t>
+          <t>change_cutoff:10.0.49-PQU-3</t>
         </is>
       </c>
     </row>
@@ -14670,16 +15598,16 @@
         <v>46330</v>
       </c>
       <c r="B153" s="8" t="n">
-        <v>46330</v>
+        <v>46354</v>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-16 change cutoff</t>
+          <t>10.0.47 PQU-16 train</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
@@ -14706,7 +15634,7 @@
       </c>
       <c r="K153" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.47-PQU-16</t>
+          <t>train_window:10.0.47-PQU-16</t>
         </is>
       </c>
     </row>
@@ -14715,16 +15643,16 @@
         <v>46330</v>
       </c>
       <c r="B154" s="8" t="n">
-        <v>46330</v>
+        <v>46354</v>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-3 change cutoff</t>
+          <t>10.0.49 PQU-3 train</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff</t>
+          <t>train_window</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -14751,97 +15679,101 @@
       </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
-          <t>change_cutoff:10.0.49-PQU-3</t>
+          <t>train_window:10.0.49-PQU-3</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="n">
-        <v>46330</v>
+        <v>46333</v>
       </c>
       <c r="B155" s="8" t="n">
-        <v>46354</v>
+        <v>46334</v>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>10.0.47 PQU-16 train</t>
+          <t>10.0.48 PQU-8 · Station 5 production</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>10.0.47-PQU-16</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>10.0.47</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="n"/>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I155" s="7" t="inlineStr"/>
       <c r="J155" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K155" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.47-PQU-16</t>
+          <t>production_window:10.0.48-PQU-8:station-5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>46330</v>
+        <v>46333</v>
       </c>
       <c r="B156" s="8" t="n">
-        <v>46354</v>
+        <v>46334</v>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>10.0.49 PQU-3 train</t>
+          <t>10.0.48 PQU-8 · Station 6 production</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>train_window</t>
+          <t>production_window</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-3</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="G156" s="7" t="n"/>
+          <t>10.0.48</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="I156" s="7" t="inlineStr"/>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#high-level-pqu-train-schedule</t>
+          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule#schedule</t>
         </is>
       </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
-          <t>train_window:10.0.49-PQU-3</t>
+          <t>production_window:10.0.48-PQU-8:station-6</t>
         </is>
       </c>
     </row>
@@ -18079,7 +19011,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -18161,7 +19093,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -18243,7 +19175,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -18325,7 +19257,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -18407,7 +19339,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -18489,7 +19421,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -18571,7 +19503,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -18653,7 +19585,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -18735,7 +19667,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -18809,7 +19741,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -18891,7 +19823,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -18973,7 +19905,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -19055,7 +19987,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -19137,7 +20069,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -19219,7 +20151,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -19301,7 +20233,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -19383,7 +20315,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -19465,7 +20397,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -19547,7 +20479,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -19629,7 +20561,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -19715,7 +20647,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -19801,7 +20733,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -19875,7 +20807,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -19949,7 +20881,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -20023,7 +20955,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -20105,7 +21037,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -20187,7 +21119,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -20269,7 +21201,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -20351,7 +21283,7 @@
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -20433,7 +21365,7 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -20484,9 +21416,9 @@
       <c r="G32" s="8" t="n">
         <v>46305</v>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -20499,13 +21431,9 @@
           <t>7.0.7996.119</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>10.0.48.7</t>
-        </is>
-      </c>
+      <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
@@ -20519,22 +21447,22 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
           <t>2026-09-24T12:00:00Z</t>
         </is>
       </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:00:00Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
       <c r="S32" s="7" t="b">
@@ -20605,7 +21533,7 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -20624,7 +21552,7 @@
         </is>
       </c>
       <c r="S33" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="7" t="n"/>
     </row>
@@ -20656,16 +21584,28 @@
       <c r="G34" s="8" t="n">
         <v>46333</v>
       </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>10.0.2645.158</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>7.0.7996.126</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48.9</t>
+        </is>
+      </c>
       <c r="L34" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
@@ -20679,26 +21619,26 @@
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
+          <t>2026-10-13T13:44:17.669863Z</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
           <t>2026-09-24T12:00:00Z</t>
         </is>
       </c>
-      <c r="Q34" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:00:00Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
       <c r="S34" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="7" t="n"/>
     </row>
@@ -20753,7 +21693,7 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
@@ -20827,7 +21767,7 @@
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -20901,7 +21841,7 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -20975,7 +21915,7 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
@@ -21049,7 +21989,7 @@
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -21123,7 +22063,7 @@
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
@@ -21197,7 +22137,7 @@
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
@@ -21271,7 +22211,7 @@
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -21345,7 +22285,7 @@
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
@@ -21431,7 +22371,7 @@
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -21505,7 +22445,7 @@
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -21579,7 +22519,7 @@
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -21653,7 +22593,7 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
@@ -21727,7 +22667,7 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -21801,7 +22741,7 @@
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
@@ -21875,7 +22815,7 @@
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -21949,7 +22889,7 @@
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
@@ -22023,7 +22963,7 @@
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -22097,7 +23037,7 @@
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -22171,7 +23111,7 @@
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -22245,7 +23185,7 @@
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -22319,7 +23259,7 @@
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -22393,7 +23333,7 @@
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -22467,7 +23407,7 @@
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -22541,7 +23481,7 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -22615,7 +23555,7 @@
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -22844,7 +23784,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -22930,7 +23870,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -22956,7 +23896,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -22966,20 +23906,20 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>46305</v>
+        <v>46319</v>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
@@ -22988,17 +23928,17 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>10.0.2645.136</t>
+          <t>10.0.2645.147</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>7.0.7996.119</t>
+          <t>7.0.7996.122</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>10.0.48.7</t>
+          <t>10.0.48.8</t>
         </is>
       </c>
       <c r="L4" s="7" t="b">
@@ -23016,22 +23956,22 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
+          <t>2026-09-29T13:39:53.051448Z</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
           <t>2026-09-24T12:00:00Z</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T12:00:00Z</t>
+          <t>2026-09-29T13:39:53.051448Z</t>
         </is>
       </c>
       <c r="S4" s="7" t="b">
@@ -23042,7 +23982,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -23052,20 +23992,20 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
@@ -23074,17 +24014,17 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>10.0.2645.147</t>
+          <t>10.0.2645.158</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>7.0.7996.122</t>
+          <t>7.0.7996.126</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>10.0.48.8</t>
+          <t>10.0.48.9</t>
         </is>
       </c>
       <c r="L5" s="7" t="b">
@@ -23102,12 +24042,12 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T13:39:53.051448Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -23117,7 +24057,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T13:39:53.051448Z</t>
+          <t>2026-10-13T13:44:17.669863Z</t>
         </is>
       </c>
       <c r="S5" s="7" t="b">
@@ -23188,7 +24128,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -23227,7 +24167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23405,7 +24345,7 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -23479,7 +24419,7 @@
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -23553,7 +24493,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -23579,7 +24519,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-8</t>
+          <t>10.0.48-PQU-9</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -23589,20 +24529,20 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>PQU-8</t>
+          <t>PQU-9</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>46309</v>
+        <v>46323</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>46309</v>
+        <v>46323</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>46333</v>
+        <v>46347</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -23627,7 +24567,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -23653,7 +24593,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-9</t>
+          <t>10.0.48-PQU-10</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -23663,20 +24603,20 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>PQU-9</t>
+          <t>PQU-10</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46323</v>
+        <v>46337</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>46347</v>
+        <v>46361</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -23701,7 +24641,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -23727,7 +24667,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-10</t>
+          <t>10.0.48-PQU-11</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -23737,20 +24677,20 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>PQU-10</t>
+          <t>PQU-11</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>46337</v>
+        <v>46351</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>46337</v>
+        <v>46351</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>46361</v>
+        <v>46375</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -23775,7 +24715,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -23801,7 +24741,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-11</t>
+          <t>10.0.48-PQU-12</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -23811,20 +24751,20 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>PQU-11</t>
+          <t>PQU-12</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>46351</v>
+        <v>46365</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>46351</v>
+        <v>46365</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>46375</v>
+        <v>46389</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -23849,7 +24789,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -23875,7 +24815,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-12</t>
+          <t>10.0.48-PQU-13</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -23885,20 +24825,20 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>PQU-12</t>
+          <t>PQU-13</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>46365</v>
+        <v>46379</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>46365</v>
+        <v>46379</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>46389</v>
+        <v>46403</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -23923,7 +24863,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -23949,7 +24889,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-13</t>
+          <t>10.0.48-PQU-14</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -23959,20 +24899,20 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>PQU-13</t>
+          <t>PQU-14</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>46379</v>
+        <v>46393</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>46379</v>
+        <v>46393</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>46403</v>
+        <v>46417</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -23997,7 +24937,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -24023,7 +24963,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-14</t>
+          <t>10.0.48-PQU-15</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -24033,20 +24973,20 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>PQU-14</t>
+          <t>PQU-15</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>46393</v>
+        <v>46407</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>46393</v>
+        <v>46407</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>46417</v>
+        <v>46431</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -24071,7 +25011,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -24097,7 +25037,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-15</t>
+          <t>10.0.48-PQU-16</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -24107,20 +25047,20 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>PQU-15</t>
+          <t>PQU-16</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>46407</v>
+        <v>46421</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46407</v>
+        <v>46421</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>46431</v>
+        <v>46445</v>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -24145,7 +25085,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -24171,7 +25111,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-16</t>
+          <t>10.0.48-PQU-17</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -24181,20 +25121,20 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>PQU-16</t>
+          <t>PQU-17</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>46421</v>
+        <v>46442</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>46421</v>
+        <v>46442</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>46445</v>
+        <v>46466</v>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -24219,7 +25159,7 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -24245,30 +25185,30 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-17</t>
+          <t>10.0.49-PQU-2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>PQU-17</t>
+          <t>PQU-2</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>46442</v>
+        <v>46316</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>46442</v>
+        <v>46316</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>46466</v>
+        <v>46340</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -24293,7 +25233,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -24319,7 +25259,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-2</t>
+          <t>10.0.49-PQU-3</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -24329,20 +25269,20 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>PQU-2</t>
+          <t>PQU-3</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>46340</v>
+        <v>46354</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -24367,7 +25307,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -24393,7 +25333,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-3</t>
+          <t>10.0.49-PQU-4</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -24403,20 +25343,20 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>PQU-3</t>
+          <t>PQU-4</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>46330</v>
+        <v>46344</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>46330</v>
+        <v>46344</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>46354</v>
+        <v>46368</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
@@ -24441,7 +25381,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -24467,7 +25407,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-4</t>
+          <t>10.0.49-PQU-5</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -24477,20 +25417,20 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>PQU-4</t>
+          <t>PQU-5</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>46344</v>
+        <v>46358</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>46344</v>
+        <v>46358</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>46368</v>
+        <v>46382</v>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
@@ -24515,7 +25455,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -24541,7 +25481,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-5</t>
+          <t>10.0.49-PQU-6</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -24551,20 +25491,20 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>PQU-5</t>
+          <t>PQU-6</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>46358</v>
+        <v>46372</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>46358</v>
+        <v>46372</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>46382</v>
+        <v>46396</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
@@ -24589,7 +25529,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -24615,7 +25555,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-6</t>
+          <t>10.0.49-PQU-7</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -24625,20 +25565,20 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>46372</v>
+        <v>46386</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>46372</v>
+        <v>46386</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>46396</v>
+        <v>46410</v>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
@@ -24663,7 +25603,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -24689,7 +25629,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-7</t>
+          <t>10.0.49-PQU-8</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -24699,20 +25639,20 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>46386</v>
+        <v>46400</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>46386</v>
+        <v>46400</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>46410</v>
+        <v>46424</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
@@ -24737,7 +25677,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -24763,7 +25703,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-8</t>
+          <t>10.0.49-PQU-9</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -24773,20 +25713,20 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>PQU-8</t>
+          <t>PQU-9</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>46400</v>
+        <v>46414</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>46400</v>
+        <v>46414</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>46424</v>
+        <v>46438</v>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
@@ -24811,7 +25751,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -24837,7 +25777,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-9</t>
+          <t>10.0.49-PQU-10</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -24847,20 +25787,20 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>PQU-9</t>
+          <t>PQU-10</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>46414</v>
+        <v>46428</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>46414</v>
+        <v>46428</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>46438</v>
+        <v>46452</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
@@ -24885,7 +25825,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -24911,7 +25851,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-10</t>
+          <t>10.0.49-PQU-11</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -24921,20 +25861,20 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>PQU-10</t>
+          <t>PQU-11</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>46428</v>
+        <v>46442</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>46428</v>
+        <v>46442</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>46452</v>
+        <v>46466</v>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
@@ -24959,7 +25899,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -24985,7 +25925,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-11</t>
+          <t>10.0.49-PQU-12</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -24995,20 +25935,20 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>PQU-11</t>
+          <t>PQU-12</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>46442</v>
+        <v>46456</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>46442</v>
+        <v>46456</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>46466</v>
+        <v>46480</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
@@ -25033,7 +25973,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -25059,7 +25999,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-12</t>
+          <t>10.0.49-PQU-13</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -25069,20 +26009,20 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>PQU-12</t>
+          <t>PQU-13</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>46456</v>
+        <v>46470</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>46456</v>
+        <v>46470</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>46480</v>
+        <v>46494</v>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
@@ -25107,7 +26047,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -25133,7 +26073,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-13</t>
+          <t>10.0.49-PQU-14</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -25143,20 +26083,20 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>PQU-13</t>
+          <t>PQU-14</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>46470</v>
+        <v>46484</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>46470</v>
+        <v>46484</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>46494</v>
+        <v>46508</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
@@ -25181,7 +26121,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -25207,7 +26147,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-14</t>
+          <t>10.0.49-PQU-15</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -25217,20 +26157,20 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>PQU-14</t>
+          <t>PQU-15</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>46484</v>
+        <v>46498</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>46484</v>
+        <v>46498</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>46508</v>
+        <v>46522</v>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -25255,7 +26195,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -25281,7 +26221,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-15</t>
+          <t>10.0.49-PQU-16</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -25291,20 +26231,20 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>PQU-15</t>
+          <t>PQU-16</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>46498</v>
+        <v>46512</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>46498</v>
+        <v>46512</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>46522</v>
+        <v>46536</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
@@ -25329,7 +26269,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -25355,7 +26295,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>10.0.49-PQU-16</t>
+          <t>10.0.49-PQU-17</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -25365,20 +26305,20 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>PQU-16</t>
+          <t>PQU-17</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>46512</v>
+        <v>46533</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>46512</v>
+        <v>46533</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>46536</v>
+        <v>46557</v>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -25403,7 +26343,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -25425,80 +26365,6 @@
         <v>0</v>
       </c>
       <c r="T29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>10.0.49-PQU-17</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>10.0.49</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>PQU-17</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>46533</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>46533</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>46557</v>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/en-us/dynamics365/fin-ops-core/dev-itpro/get-started/quality-updates-schedule</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25617,7 +26483,7 @@
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25659,7 +26525,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25701,7 +26567,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25743,7 +26609,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25785,7 +26651,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25827,7 +26693,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25865,7 +26731,7 @@
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25907,7 +26773,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25949,7 +26815,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -25991,7 +26857,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26033,7 +26899,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26075,14 +26941,14 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -26092,7 +26958,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -26104,23 +26970,23 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>46284</v>
+        <v>46298</v>
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -26130,7 +26996,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -26142,27 +27008,27 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>46286</v>
+        <v>46300</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>46289</v>
+        <v>46303</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>46292</v>
+        <v>46306</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -26172,7 +27038,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -26184,27 +27050,27 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>46286</v>
+        <v>46300</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>46289</v>
+        <v>46303</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>46292</v>
+        <v>46306</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -26214,7 +27080,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -26226,27 +27092,27 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>46293</v>
+        <v>46307</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>46296</v>
+        <v>46310</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>46298</v>
+        <v>46312</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -26256,7 +27122,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -26268,27 +27134,27 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>46303</v>
+        <v>46317</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>46305</v>
+        <v>46319</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-6</t>
+          <t>10.0.48-PQU-7</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -26298,7 +27164,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PQU-6</t>
+          <t>PQU-7</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -26310,27 +27176,27 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>46303</v>
+        <v>46317</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>46305</v>
+        <v>46319</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -26340,7 +27206,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -26352,23 +27218,23 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>46298</v>
+        <v>46312</v>
       </c>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -26378,7 +27244,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -26390,27 +27256,27 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>46303</v>
+        <v>46317</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>46305</v>
+        <v>46319</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -26420,7 +27286,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
@@ -26432,27 +27298,27 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>46303</v>
+        <v>46317</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>46305</v>
+        <v>46319</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -26462,7 +27328,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -26474,27 +27340,27 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>46307</v>
+        <v>46321</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>46310</v>
+        <v>46324</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>46312</v>
+        <v>46326</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -26504,7 +27370,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -26516,27 +27382,27 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>46317</v>
+        <v>46331</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>10.0.48-PQU-7</t>
+          <t>10.0.48-PQU-8</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -26546,7 +27412,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>PQU-7</t>
+          <t>PQU-8</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -26558,20 +27424,20 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>46317</v>
+        <v>46331</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26609,7 +27475,7 @@
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26651,7 +27517,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26693,7 +27559,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26735,7 +27601,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26777,7 +27643,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -26819,7 +27685,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>aee43141bb5f24e63c1e63805dcd9e1c5452c334</t>
+          <t>7d86a35169692606d303c21e204ae6032d44d44e</t>
         </is>
       </c>
     </row>
@@ -28572,9 +29438,9 @@
           <t>10.0.2645.136</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
@@ -28629,10 +29495,14 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>10.0.2645.158</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
@@ -30346,9 +31216,9 @@
           <t>7.0.7996.119</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
@@ -30403,10 +31273,14 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>7.0.7996.126</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
@@ -32019,14 +32893,10 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>10.0.48.7</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>In-Progress</t>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
@@ -32081,10 +32951,14 @@
           <t>10.0.48</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>10.0.48.9</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>In-Progress</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -389,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataQuality" displayName="DataQuality" ref="A1:E4" headerRowCount="1">
-  <autoFilter ref="A1:E4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataQuality" displayName="DataQuality" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Severity"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863Z</t>
+          <t>2026-10-15T04:35:05.363122Z</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863+00:00</t>
+          <t>2026-10-15T04:35:05.363122+00:00</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>stale</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863Z</t>
+          <t>2026-10-15T04:35:05.363122Z</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863Z</t>
+          <t>2026-10-15T04:35:05.363122Z</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863Z</t>
+          <t>2026-10-15T04:35:05.363122Z</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T13:44:17.669863Z</t>
+          <t>2026-10-15T04:35:05.363122Z</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5854,7 +5854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5921,25 +5921,21 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>maintenance-geo-unmapped</t>
+          <t>source-stale</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Microsoft's planned maintenance window table does not list a geography for DoD, so no maintenance window is shown for it.</t>
+          <t>Service update availability could not be refreshed (Could not download https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/772dd937f34b393df7a2cd03864bb077aaabe2c2/articles/fin-ops-core/dev-itpro/get-started/public-preview-releases.md: HTTP Error 429: Too Many Requests); showing the last published copy (commit b348d4818418, 2026-10-08).</t>
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>region.DoD</t>
-        </is>
-      </c>
+      <c r="E3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -5954,11 +5950,34 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Microsoft's planned maintenance window table does not list a geography for Government Community Cloud, so no maintenance window is shown for it.</t>
+          <t>Microsoft's planned maintenance window table does not list a geography for DoD, so no maintenance window is shown for it.</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>region.DoD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>maintenance-geo-unmapped</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft's planned maintenance window table does not list a geography for Government Community Cloud, so no maintenance window is shown for it.</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>region.Government Community Cloud</t>
         </is>

--- a/excel/D365-PQU-Tracker.xlsx
+++ b/excel/D365-PQU-Tracker.xlsx
@@ -389,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataQuality" displayName="DataQuality" ref="A1:E5" headerRowCount="1">
-  <autoFilter ref="A1:E5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataQuality" displayName="DataQuality" ref="A1:E4" headerRowCount="1">
+  <autoFilter ref="A1:E4"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Severity"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122Z</t>
+          <t>2026-10-15T04:44:14.760710Z</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122+00:00</t>
+          <t>2026-10-15T04:44:14.760710+00:00</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>current</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122Z</t>
+          <t>2026-10-15T04:44:14.760710Z</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122Z</t>
+          <t>2026-10-15T04:44:14.760710Z</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122Z</t>
+          <t>2026-10-15T04:44:14.760710Z</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T04:35:05.363122Z</t>
+          <t>2026-10-15T04:44:14.760710Z</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5854,7 +5854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5921,21 +5921,25 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>source-stale</t>
+          <t>maintenance-geo-unmapped</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Service update availability could not be refreshed (Could not download https://raw.githubusercontent.com/MicrosoftDocs/dynamics-365-unified-operations-public/772dd937f34b393df7a2cd03864bb077aaabe2c2/articles/fin-ops-core/dev-itpro/get-started/public-preview-releases.md: HTTP Error 429: Too Many Requests); showing the last published copy (commit b348d4818418, 2026-10-08).</t>
+          <t>Microsoft's planned maintenance window table does not list a geography for DoD, so no maintenance window is shown for it.</t>
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>region.DoD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -5950,34 +5954,11 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Microsoft's planned maintenance window table does not list a geography for DoD, so no maintenance window is shown for it.</t>
+          <t>Microsoft's planned maintenance window table does not list a geography for Government Community Cloud, so no maintenance window is shown for it.</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>region.DoD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>maintenance-geo-unmapped</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Microsoft's planned maintenance window table does not list a geography for Government Community Cloud, so no maintenance window is shown for it.</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>region.Government Community Cloud</t>
         </is>
@@ -6100,7 +6081,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6119,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6157,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6195,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6233,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6271,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6309,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6347,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6385,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>b348d48184186e3244de6aae50a1377c5718789f</t>
+          <t>772dd937f34b393df7a2cd03864bb077aaabe2c2</t>
         </is>
       </c>
     </row>
